--- a/astro-site/public/dl/kit-tareas-catering/BONUS-02-calendario-anual-tareas.xlsx
+++ b/astro-site/public/dl/kit-tareas-catering/BONUS-02-calendario-anual-tareas.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Calendario" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calendario" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Calendario'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -151,54 +153,54 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="18">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="7" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="8" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="9" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -558,15 +560,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -574,6 +577,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -602,9 +606,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -626,8 +628,25 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-catering · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -636,17 +655,17 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="30"/>
-    <col customWidth="1" max="3" min="3" width="18"/>
-    <col customWidth="1" max="4" min="4" width="35"/>
-    <col customWidth="1" max="5" min="5" width="20"/>
-    <col customWidth="1" max="6" min="6" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -663,6 +682,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1220,6 +1240,15 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-catering/BONUS-02-calendario-anual-tareas.xlsx
+++ b/astro-site/public/dl/kit-tareas-catering/BONUS-02-calendario-anual-tareas.xlsx
@@ -562,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -588,7 +588,7 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>▸ Las 20 fechas clave del año para empresas de catering.</t>
+          <t>▸ Las 22 fechas clave del año para empresas de catering.</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,14 @@
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-catering · info@aichef.pro</t>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-catering · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -657,7 +664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -678,7 +685,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>AI Chef Pro · aichef.pro — 20 fechas clave para planificar tu año</t>
+          <t>AI Chef Pro · aichef.pro — 22 fechas clave para planificar tu año</t>
         </is>
       </c>
     </row>
@@ -799,17 +806,17 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Abril — Semana Santa</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
+          <t>19 Mar — Día del Padre</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>Festividad</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>Menús sin carne, bacalao, potajes, postres tradicionales</t>
+          <t>Comidas familiares de mediodía y detalles de empresa; menús cerrados y tartas por encargo</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -825,22 +832,22 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Mayo — Temporada de bodas (inicio)</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>Boda</t>
+          <t>Abril — Semana Santa</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Festividad</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Alta demanda de personal eventual, reservar proveedores</t>
+          <t>Menús sin carne, bacalao, potajes, postres tradicionales</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>6-12 meses</t>
+          <t>3 semanas</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -851,22 +858,22 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Mayo — Comuniones (pico)</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>Celebración</t>
+          <t>Mayo — Temporada de bodas (inicio)</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>Boda</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>Máxima demanda: 2-3 eventos simultáneos posibles</t>
+          <t>Alta demanda de personal eventual, reservar proveedores</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>3-4 meses</t>
+          <t>6-12 meses</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -877,22 +884,22 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Junio — Bodas + Graduaciones</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>Mixto</t>
+          <t>Mayo — Comuniones (pico)</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Celebración</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>Eventos outdoor, planes B por lluvia, carpas</t>
+          <t>Máxima demanda: 2-3 eventos simultáneos posibles</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>6-12 meses</t>
+          <t>3-4 meses</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -903,22 +910,22 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Junio — Fin de curso corporativo</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
+          <t>Junio — Bodas + Graduaciones</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Mixto</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>Team building + catering, formato cocktail outdoor</t>
+          <t>Eventos outdoor, planes B por lluvia, carpas</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>2 meses</t>
+          <t>6-12 meses</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -929,22 +936,22 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Julio-Agosto — Bodas de verano</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>Boda</t>
+          <t>Junio — Fin de curso corporativo</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>Gestión del calor, menús frescos, más personal</t>
+          <t>Team building + catering, formato cocktail outdoor</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>6-12 meses</t>
+          <t>2 meses</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -955,22 +962,22 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Septiembre — Vuelta al cole corporativa</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
+          <t>Julio-Agosto — Bodas de verano</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>Boda</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>Kick-offs, convenciones, coffee breaks masivos</t>
+          <t>Gestión del calor, menús frescos, más personal</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>1-2 meses</t>
+          <t>6-12 meses</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
@@ -981,22 +988,22 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Septiembre — Bodas de otoño (inicio)</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>Boda</t>
+          <t>Septiembre — Vuelta al cole corporativa</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>Menús de temporada otoñal, setas, caza</t>
+          <t>Kick-offs, convenciones, coffee breaks masivos</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>6-12 meses</t>
+          <t>1-2 meses</t>
         </is>
       </c>
       <c r="F15" s="12" t="n"/>
@@ -1007,22 +1014,22 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Octubre — Halloween</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Festividad</t>
+          <t>Septiembre — Bodas de otoño (inicio)</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>Boda</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>Eventos temáticos, decoración, cocktails especiales</t>
+          <t>Menús de temporada otoñal, setas, caza</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>4 semanas</t>
+          <t>6-12 meses</t>
         </is>
       </c>
       <c r="F16" s="12" t="n"/>
@@ -1033,22 +1040,22 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Octubre — Cenas de empresa (inicio)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
+          <t>Octubre — Halloween</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Festividad</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>Presupuestos para diciembre, reservas anticipadas</t>
+          <t>Eventos temáticos, decoración, cocktails especiales</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>2-3 meses</t>
+          <t>4 semanas</t>
         </is>
       </c>
       <c r="F17" s="12" t="n"/>
@@ -1059,22 +1066,22 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Noviembre — Black Friday gastro</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>Comercial</t>
+          <t>Octubre — Cenas de empresa (inicio)</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>Ofertas de packs de catering para empresas</t>
+          <t>Presupuestos para diciembre, reservas anticipadas</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>4 semanas</t>
+          <t>2-3 meses</t>
         </is>
       </c>
       <c r="F18" s="12" t="n"/>
@@ -1085,22 +1092,22 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Diciembre — Cenas de Navidad empresa</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>Corporativo</t>
+          <t>Noviembre — Black Friday gastro</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>Comercial</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>Máxima demanda corporativa del año. Personal extra</t>
+          <t>Ofertas de packs de catering para empresas</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>2-3 meses</t>
+          <t>4 semanas</t>
         </is>
       </c>
       <c r="F19" s="12" t="n"/>
@@ -1111,22 +1118,22 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Diciembre — Comidas de Navidad familia</t>
-        </is>
-      </c>
-      <c r="C20" s="13" t="inlineStr">
-        <is>
-          <t>Celebración</t>
+          <t>6-8 Dic — Puente de la Constitución</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>Mixto</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>Menús navideños, cordero, marisco, turrones</t>
+          <t>Tres días seguidos de eventos: bodas de invierno, cenas de empresa adelantadas y comidas familiares. Cerrar personal eventual y stock ANTES del puente</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>4-6 semanas</t>
+          <t>4 semanas</t>
         </is>
       </c>
       <c r="F20" s="12" t="n"/>
@@ -1137,17 +1144,17 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>31 Dic — Nochevieja / Cotillón</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>Festividad</t>
+          <t>Diciembre — Cenas de Navidad empresa</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>Menú premium, cotillón, barra libre, uvas</t>
+          <t>Máxima demanda corporativa del año. Personal extra</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
@@ -1163,7 +1170,7 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Todo el año — Bautizos</t>
+          <t>Diciembre — Comidas de Navidad familia</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
@@ -1173,12 +1180,12 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>Formato cocktail o sentado, menú infantil + adulto</t>
+          <t>Menús navideños, cordero, marisco, turrones</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>1-2 meses</t>
+          <t>4-6 semanas</t>
         </is>
       </c>
       <c r="F22" s="12" t="n"/>
@@ -1189,22 +1196,22 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Todo el año — Funerales / Tanatorio</t>
-        </is>
-      </c>
-      <c r="C23" s="13" t="inlineStr">
-        <is>
-          <t>Celebración</t>
+          <t>31 Dic — Nochevieja / Cotillón</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Festividad</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>Servicio discreto, coffee + canapés, entrega rápida</t>
+          <t>Menú premium, cotillón, barra libre, uvas</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>24-48h</t>
+          <t>2-3 meses</t>
         </is>
       </c>
       <c r="F23" s="12" t="n"/>
@@ -1215,25 +1222,77 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
+          <t>Todo el año — Bautizos</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>Celebración</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>Formato cocktail o sentado, menú infantil + adulto</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>1-2 meses</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Todo el año — Funerales / Tanatorio</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>Celebración</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>Servicio discreto, coffee + canapés, entrega rápida</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>24-48h</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
           <t>Todo el año — Presentaciones producto</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C26" s="16" t="inlineStr">
         <is>
           <t>Corporativo</t>
         </is>
       </c>
-      <c r="D24" s="10" t="inlineStr">
+      <c r="D26" s="10" t="inlineStr">
         <is>
           <t>Branding del cliente, finger food premium, AV</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E26" s="11" t="inlineStr">
         <is>
           <t>3-6 semanas</t>
         </is>
       </c>
-      <c r="F24" s="12" t="n"/>
+      <c r="F26" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
